--- a/data/H131_20260618_12.xlsx
+++ b/data/H131_20260618_12.xlsx
@@ -348,7 +348,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="21" width="8.71"/>
+    <col customWidth="1" min="1" max="9" width="8.71"/>
+    <col customWidth="1" min="10" max="10" width="16.29"/>
+    <col customWidth="1" min="11" max="21" width="8.71"/>
     <col customWidth="1" min="22" max="22" width="10.71"/>
     <col customWidth="1" min="23" max="23" width="9.0"/>
     <col customWidth="1" min="24" max="26" width="8.71"/>
@@ -596,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>592.0</v>
+        <v>595.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -608,10 +610,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>592.0</v>
+        <v>595.0</v>
       </c>
       <c r="O4" s="2">
-        <v>261.0</v>
+        <v>264.0</v>
       </c>
       <c r="P4" s="2">
         <v>331.0</v>
@@ -738,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>662.0</v>
+        <v>671.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -750,13 +752,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>662.0</v>
+        <v>671.0</v>
       </c>
       <c r="O6" s="2">
-        <v>309.0</v>
+        <v>317.0</v>
       </c>
       <c r="P6" s="2">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0</v>
@@ -951,7 +953,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>415.0</v>
+        <v>419.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -963,13 +965,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>415.0</v>
+        <v>419.0</v>
       </c>
       <c r="O9" s="2">
-        <v>214.0</v>
+        <v>217.0</v>
       </c>
       <c r="P9" s="2">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="Q9" s="2">
         <v>0.0</v>
@@ -1235,7 +1237,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" s="2">
-        <v>960.0</v>
+        <v>1004.0</v>
       </c>
       <c r="K13" s="2">
         <v>1.0</v>
@@ -1247,13 +1249,13 @@
         <v>0.0</v>
       </c>
       <c r="N13" s="2">
-        <v>960.0</v>
+        <v>1004.0</v>
       </c>
       <c r="O13" s="2">
-        <v>493.0</v>
+        <v>523.0</v>
       </c>
       <c r="P13" s="2">
-        <v>467.0</v>
+        <v>481.0</v>
       </c>
       <c r="Q13" s="2">
         <v>0.0</v>
@@ -1306,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>656.0</v>
+        <v>669.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1318,10 +1320,10 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>656.0</v>
+        <v>669.0</v>
       </c>
       <c r="O14" s="2">
-        <v>269.0</v>
+        <v>282.0</v>
       </c>
       <c r="P14" s="2">
         <v>387.0</v>
@@ -1377,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>401.0</v>
+        <v>449.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1389,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>401.0</v>
+        <v>449.0</v>
       </c>
       <c r="O15" s="2">
-        <v>164.0</v>
+        <v>198.0</v>
       </c>
       <c r="P15" s="2">
-        <v>237.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1448,7 +1450,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1460,10 +1462,10 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
       <c r="O16" s="2">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="P16" s="2">
         <v>284.0</v>
@@ -1661,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>581.0</v>
+        <v>609.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1673,13 +1675,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>581.0</v>
+        <v>609.0</v>
       </c>
       <c r="O19" s="2">
-        <v>301.0</v>
+        <v>319.0</v>
       </c>
       <c r="P19" s="2">
-        <v>280.0</v>
+        <v>290.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
@@ -1762,7 +1764,7 @@
         <v>16.0</v>
       </c>
       <c r="T20" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U20" s="2">
         <v>0.0</v>
@@ -1771,7 +1773,7 @@
         <v>0.0</v>
       </c>
       <c r="W20" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -2016,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>564.0</v>
+        <v>570.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2028,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>564.0</v>
+        <v>570.0</v>
       </c>
       <c r="O24" s="2">
-        <v>319.0</v>
+        <v>323.0</v>
       </c>
       <c r="P24" s="2">
-        <v>230.0</v>
+        <v>232.0</v>
       </c>
       <c r="Q24" s="2">
         <v>15.0</v>
@@ -2087,7 +2089,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2099,10 +2101,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="O25" s="2">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="P25" s="2">
         <v>88.0</v>
@@ -2300,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>976.0</v>
+        <v>979.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2312,13 +2314,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>976.0</v>
+        <v>979.0</v>
       </c>
       <c r="O28" s="2">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="P28" s="2">
-        <v>449.0</v>
+        <v>450.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
@@ -2513,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>605.0</v>
+        <v>635.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2525,13 +2527,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>605.0</v>
+        <v>635.0</v>
       </c>
       <c r="O31" s="2">
-        <v>299.0</v>
+        <v>318.0</v>
       </c>
       <c r="P31" s="2">
-        <v>301.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q31" s="2">
         <v>5.0</v>
@@ -2584,7 +2586,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>659.0</v>
+        <v>669.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2596,13 +2598,13 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>659.0</v>
+        <v>669.0</v>
       </c>
       <c r="O32" s="2">
-        <v>313.0</v>
+        <v>318.0</v>
       </c>
       <c r="P32" s="2">
-        <v>329.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q32" s="2">
         <v>17.0</v>
@@ -2655,7 +2657,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" s="2">
-        <v>298.0</v>
+        <v>304.0</v>
       </c>
       <c r="K33" s="2">
         <v>1.0</v>
@@ -2667,10 +2669,10 @@
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <v>298.0</v>
+        <v>304.0</v>
       </c>
       <c r="O33" s="2">
-        <v>130.0</v>
+        <v>136.0</v>
       </c>
       <c r="P33" s="2">
         <v>168.0</v>
@@ -2679,10 +2681,10 @@
         <v>0.0</v>
       </c>
       <c r="R33" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="S33" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="T33" s="2">
         <v>0.0</v>
@@ -2694,7 +2696,7 @@
         <v>0.0</v>
       </c>
       <c r="W33" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -2726,7 +2728,7 @@
         <v>647.0</v>
       </c>
       <c r="J34" s="2">
-        <v>576.0</v>
+        <v>581.0</v>
       </c>
       <c r="K34" s="2">
         <v>1.0</v>
@@ -2738,10 +2740,10 @@
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <v>576.0</v>
+        <v>581.0</v>
       </c>
       <c r="O34" s="2">
-        <v>314.0</v>
+        <v>319.0</v>
       </c>
       <c r="P34" s="2">
         <v>262.0</v>
@@ -2750,7 +2752,7 @@
         <v>0.0</v>
       </c>
       <c r="R34" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="S34" s="2">
         <v>2.0</v>
@@ -2765,7 +2767,7 @@
         <v>0.0</v>
       </c>
       <c r="W34" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -2797,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>347.0</v>
+        <v>359.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2809,13 +2811,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>347.0</v>
+        <v>359.0</v>
       </c>
       <c r="O35" s="2">
-        <v>177.0</v>
+        <v>183.0</v>
       </c>
       <c r="P35" s="2">
-        <v>161.0</v>
+        <v>167.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
@@ -2892,22 +2894,22 @@
         <v>0.0</v>
       </c>
       <c r="R36" s="2">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
       <c r="S36" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="T36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="U36" s="2">
         <v>9.0</v>
       </c>
-      <c r="T36" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="U36" s="2">
-        <v>3.0</v>
-      </c>
       <c r="V36" s="2">
         <v>0.0</v>
       </c>
       <c r="W36" s="2">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -2939,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2951,10 +2953,10 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="O37" s="2">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="P37" s="2">
         <v>204.0</v>
@@ -3081,7 +3083,7 @@
         <v>585.0</v>
       </c>
       <c r="J39" s="2">
-        <v>349.0</v>
+        <v>400.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3093,22 +3095,22 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>349.0</v>
+        <v>400.0</v>
       </c>
       <c r="O39" s="2">
-        <v>176.0</v>
+        <v>199.0</v>
       </c>
       <c r="P39" s="2">
-        <v>173.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
       </c>
       <c r="R39" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="S39" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="T39" s="2">
         <v>0.0</v>
@@ -3120,7 +3122,7 @@
         <v>0.0</v>
       </c>
       <c r="W39" s="2">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -3152,7 +3154,7 @@
         <v>1249.0</v>
       </c>
       <c r="J40" s="2">
-        <v>1136.0</v>
+        <v>1147.0</v>
       </c>
       <c r="K40" s="2">
         <v>1.0</v>
@@ -3164,10 +3166,10 @@
         <v>0.0</v>
       </c>
       <c r="N40" s="2">
-        <v>1136.0</v>
+        <v>1147.0</v>
       </c>
       <c r="O40" s="2">
-        <v>639.0</v>
+        <v>650.0</v>
       </c>
       <c r="P40" s="2">
         <v>490.0</v>
@@ -3294,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>408.0</v>
+        <v>422.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3306,13 +3308,13 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>408.0</v>
+        <v>422.0</v>
       </c>
       <c r="O42" s="2">
-        <v>257.0</v>
+        <v>267.0</v>
       </c>
       <c r="P42" s="2">
-        <v>151.0</v>
+        <v>155.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
@@ -3436,7 +3438,7 @@
         <v>1094.0</v>
       </c>
       <c r="J44" s="2">
-        <v>921.0</v>
+        <v>951.0</v>
       </c>
       <c r="K44" s="2">
         <v>1.0</v>
@@ -3448,13 +3450,13 @@
         <v>0.0</v>
       </c>
       <c r="N44" s="2">
-        <v>921.0</v>
+        <v>951.0</v>
       </c>
       <c r="O44" s="2">
-        <v>460.0</v>
+        <v>484.0</v>
       </c>
       <c r="P44" s="2">
-        <v>460.0</v>
+        <v>466.0</v>
       </c>
       <c r="Q44" s="2">
         <v>1.0</v>
@@ -3507,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>988.0</v>
+        <v>1003.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3519,34 +3521,34 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>987.0</v>
+        <v>1002.0</v>
       </c>
       <c r="O45" s="2">
-        <v>459.0</v>
+        <v>473.0</v>
       </c>
       <c r="P45" s="2">
         <v>515.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R45" s="2">
         <v>48.0</v>
       </c>
       <c r="S45" s="2">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
       <c r="T45" s="2">
         <v>0.0</v>
       </c>
       <c r="U45" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="V45" s="2">
         <v>0.0</v>
       </c>
       <c r="W45" s="2">
-        <v>50.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3649,7 +3651,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" s="2">
-        <v>719.0</v>
+        <v>721.0</v>
       </c>
       <c r="K47" s="2">
         <v>1.0</v>
@@ -3661,13 +3663,13 @@
         <v>0.0</v>
       </c>
       <c r="N47" s="2">
-        <v>719.0</v>
+        <v>721.0</v>
       </c>
       <c r="O47" s="2">
         <v>393.0</v>
       </c>
       <c r="P47" s="2">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="Q47" s="2">
         <v>1.0</v>
@@ -3720,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>854.0</v>
+        <v>876.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3732,10 +3734,10 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>854.0</v>
+        <v>876.0</v>
       </c>
       <c r="O48" s="2">
-        <v>479.0</v>
+        <v>501.0</v>
       </c>
       <c r="P48" s="2">
         <v>375.0</v>
@@ -3791,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>904.0</v>
+        <v>905.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3803,22 +3805,22 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>904.0</v>
+        <v>905.0</v>
       </c>
       <c r="O49" s="2">
         <v>471.0</v>
       </c>
       <c r="P49" s="2">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="Q49" s="2">
         <v>0.0</v>
       </c>
       <c r="R49" s="2">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="S49" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T49" s="2">
         <v>0.0</v>
@@ -3830,7 +3832,7 @@
         <v>0.0</v>
       </c>
       <c r="W49" s="2">
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -4146,7 +4148,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>521.0</v>
+        <v>555.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4158,13 +4160,13 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>521.0</v>
+        <v>555.0</v>
       </c>
       <c r="O54" s="2">
-        <v>274.0</v>
+        <v>293.0</v>
       </c>
       <c r="P54" s="2">
-        <v>247.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q54" s="2">
         <v>0.0</v>
@@ -4359,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>471.0</v>
+        <v>480.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4371,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>471.0</v>
+        <v>480.0</v>
       </c>
       <c r="O57" s="2">
-        <v>471.0</v>
+        <v>480.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4430,7 +4432,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>646.0</v>
+        <v>649.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4442,10 +4444,10 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>646.0</v>
+        <v>649.0</v>
       </c>
       <c r="O58" s="2">
-        <v>299.0</v>
+        <v>302.0</v>
       </c>
       <c r="P58" s="2">
         <v>347.0</v>
@@ -4501,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>571.0</v>
+        <v>574.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4513,10 +4515,10 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>571.0</v>
+        <v>574.0</v>
       </c>
       <c r="O59" s="2">
-        <v>269.0</v>
+        <v>272.0</v>
       </c>
       <c r="P59" s="2">
         <v>302.0</v>
@@ -4643,7 +4645,7 @@
         <v>1075.0</v>
       </c>
       <c r="J61" s="2">
-        <v>797.0</v>
+        <v>799.0</v>
       </c>
       <c r="K61" s="2">
         <v>1.0</v>
@@ -4655,13 +4657,13 @@
         <v>0.0</v>
       </c>
       <c r="N61" s="2">
-        <v>797.0</v>
+        <v>799.0</v>
       </c>
       <c r="O61" s="2">
-        <v>400.0</v>
+        <v>401.0</v>
       </c>
       <c r="P61" s="2">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q61" s="2">
         <v>0.0</v>
@@ -4738,7 +4740,7 @@
         <v>1.0</v>
       </c>
       <c r="R62" s="2">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="S62" s="2">
         <v>0.0</v>
@@ -4753,7 +4755,7 @@
         <v>0.0</v>
       </c>
       <c r="W62" s="2">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -4785,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>678.0</v>
+        <v>705.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4797,13 +4799,13 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>678.0</v>
+        <v>705.0</v>
       </c>
       <c r="O63" s="2">
-        <v>335.0</v>
+        <v>357.0</v>
       </c>
       <c r="P63" s="2">
-        <v>343.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q63" s="2">
         <v>0.0</v>
@@ -4998,7 +5000,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" s="2">
-        <v>1020.0</v>
+        <v>1029.0</v>
       </c>
       <c r="K66" s="2">
         <v>1.0</v>
@@ -5010,22 +5012,22 @@
         <v>0.0</v>
       </c>
       <c r="N66" s="2">
-        <v>1020.0</v>
+        <v>1029.0</v>
       </c>
       <c r="O66" s="2">
-        <v>555.0</v>
+        <v>559.0</v>
       </c>
       <c r="P66" s="2">
-        <v>464.0</v>
+        <v>468.0</v>
       </c>
       <c r="Q66" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R66" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="S66" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="T66" s="2">
         <v>0.0</v>
@@ -5037,7 +5039,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" s="2">
-        <v>14.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -5140,7 +5142,7 @@
         <v>1042.0</v>
       </c>
       <c r="J68" s="2">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
       <c r="K68" s="2">
         <v>1.0</v>
@@ -5152,10 +5154,10 @@
         <v>0.0</v>
       </c>
       <c r="N68" s="2">
-        <v>965.0</v>
+        <v>966.0</v>
       </c>
       <c r="O68" s="2">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="P68" s="2">
         <v>439.0</v>
@@ -5208,10 +5210,10 @@
         <v>1125.0</v>
       </c>
       <c r="I69" s="2">
-        <v>1121.0</v>
+        <v>1122.0</v>
       </c>
       <c r="J69" s="2">
-        <v>923.0</v>
+        <v>957.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5223,13 +5225,13 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>922.0</v>
+        <v>956.0</v>
       </c>
       <c r="O69" s="2">
-        <v>462.0</v>
+        <v>485.0</v>
       </c>
       <c r="P69" s="2">
-        <v>461.0</v>
+        <v>472.0</v>
       </c>
       <c r="Q69" s="2">
         <v>0.0</v>
@@ -5282,7 +5284,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1001.0</v>
+        <v>1005.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5294,10 +5296,10 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1001.0</v>
+        <v>1005.0</v>
       </c>
       <c r="O70" s="2">
-        <v>621.0</v>
+        <v>625.0</v>
       </c>
       <c r="P70" s="2">
         <v>371.0</v>
@@ -5495,7 +5497,7 @@
         <v>973.0</v>
       </c>
       <c r="J73" s="2">
-        <v>881.0</v>
+        <v>909.0</v>
       </c>
       <c r="K73" s="2">
         <v>1.0</v>
@@ -5507,13 +5509,13 @@
         <v>0.0</v>
       </c>
       <c r="N73" s="2">
-        <v>881.0</v>
+        <v>909.0</v>
       </c>
       <c r="O73" s="2">
-        <v>433.0</v>
+        <v>459.0</v>
       </c>
       <c r="P73" s="2">
-        <v>441.0</v>
+        <v>443.0</v>
       </c>
       <c r="Q73" s="2">
         <v>7.0</v>
@@ -5637,7 +5639,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>787.0</v>
+        <v>801.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5649,16 +5651,16 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>787.0</v>
+        <v>801.0</v>
       </c>
       <c r="O75" s="2">
-        <v>413.0</v>
+        <v>416.0</v>
       </c>
       <c r="P75" s="2">
-        <v>373.0</v>
+        <v>377.0</v>
       </c>
       <c r="Q75" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="R75" s="2">
         <v>4.0</v>
@@ -5921,7 +5923,7 @@
         <v>786.0</v>
       </c>
       <c r="J79" s="2">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5933,10 +5935,10 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="O79" s="2">
-        <v>102.0</v>
+        <v>104.0</v>
       </c>
       <c r="P79" s="2">
         <v>212.0</v>
@@ -6063,7 +6065,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" s="2">
-        <v>667.0</v>
+        <v>677.0</v>
       </c>
       <c r="K81" s="2">
         <v>1.0</v>
@@ -6075,19 +6077,19 @@
         <v>0.0</v>
       </c>
       <c r="N81" s="2">
-        <v>667.0</v>
+        <v>677.0</v>
       </c>
       <c r="O81" s="2">
-        <v>346.0</v>
+        <v>354.0</v>
       </c>
       <c r="P81" s="2">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q81" s="2">
         <v>0.0</v>
       </c>
       <c r="R81" s="2">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="S81" s="2">
         <v>19.0</v>
@@ -6102,7 +6104,7 @@
         <v>0.0</v>
       </c>
       <c r="W81" s="2">
-        <v>30.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -6347,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1063.0</v>
+        <v>1076.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6359,13 +6361,13 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1063.0</v>
+        <v>1076.0</v>
       </c>
       <c r="O85" s="2">
-        <v>507.0</v>
+        <v>519.0</v>
       </c>
       <c r="P85" s="2">
-        <v>556.0</v>
+        <v>557.0</v>
       </c>
       <c r="Q85" s="2">
         <v>0.0</v>
@@ -6418,7 +6420,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>877.0</v>
+        <v>884.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6430,13 +6432,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>877.0</v>
+        <v>884.0</v>
       </c>
       <c r="O86" s="2">
-        <v>413.0</v>
+        <v>417.0</v>
       </c>
       <c r="P86" s="2">
-        <v>464.0</v>
+        <v>467.0</v>
       </c>
       <c r="Q86" s="2">
         <v>0.0</v>
@@ -6560,7 +6562,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" s="2">
-        <v>596.0</v>
+        <v>606.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6572,13 +6574,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>596.0</v>
+        <v>606.0</v>
       </c>
       <c r="O88" s="2">
-        <v>277.0</v>
+        <v>281.0</v>
       </c>
       <c r="P88" s="2">
-        <v>319.0</v>
+        <v>325.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
@@ -6702,7 +6704,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" s="2">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
       <c r="K90" s="2">
         <v>1.0</v>
@@ -6714,7 +6716,7 @@
         <v>0.0</v>
       </c>
       <c r="N90" s="2">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
       <c r="O90" s="2">
         <v>336.0</v>
@@ -6723,7 +6725,7 @@
         <v>321.0</v>
       </c>
       <c r="Q90" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R90" s="2">
         <v>14.0</v>
@@ -6773,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>621.0</v>
+        <v>631.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6785,34 +6787,34 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>621.0</v>
+        <v>631.0</v>
       </c>
       <c r="O91" s="2">
-        <v>124.0</v>
+        <v>126.0</v>
       </c>
       <c r="P91" s="2">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>185.0</v>
+        <v>192.0</v>
       </c>
       <c r="R91" s="2">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="S91" s="2">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="T91" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U91" s="2">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="V91" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>57.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6844,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>591.0</v>
+        <v>612.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6856,16 +6858,16 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>591.0</v>
+        <v>612.0</v>
       </c>
       <c r="O92" s="2">
-        <v>241.0</v>
+        <v>255.0</v>
       </c>
       <c r="P92" s="2">
-        <v>267.0</v>
+        <v>272.0</v>
       </c>
       <c r="Q92" s="2">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="R92" s="2">
         <v>43.0</v>
@@ -6915,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>717.0</v>
+        <v>720.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6927,10 +6929,10 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>717.0</v>
+        <v>720.0</v>
       </c>
       <c r="O93" s="2">
-        <v>395.0</v>
+        <v>398.0</v>
       </c>
       <c r="P93" s="2">
         <v>321.0</v>
@@ -6986,7 +6988,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>531.0</v>
+        <v>540.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -6998,13 +7000,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>531.0</v>
+        <v>540.0</v>
       </c>
       <c r="O94" s="2">
-        <v>231.0</v>
+        <v>237.0</v>
       </c>
       <c r="P94" s="2">
-        <v>300.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q94" s="2">
         <v>0.0</v>
@@ -7057,7 +7059,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" s="2">
-        <v>1241.0</v>
+        <v>1246.0</v>
       </c>
       <c r="K95" s="2">
         <v>1.0</v>
@@ -7069,10 +7071,10 @@
         <v>0.0</v>
       </c>
       <c r="N95" s="2">
-        <v>1241.0</v>
+        <v>1246.0</v>
       </c>
       <c r="O95" s="2">
-        <v>596.0</v>
+        <v>601.0</v>
       </c>
       <c r="P95" s="2">
         <v>645.0</v>
@@ -7128,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>699.0</v>
+        <v>702.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7140,10 +7142,10 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>699.0</v>
+        <v>702.0</v>
       </c>
       <c r="O96" s="2">
-        <v>347.0</v>
+        <v>350.0</v>
       </c>
       <c r="P96" s="2">
         <v>352.0</v>
@@ -7270,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>330.0</v>
+        <v>348.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7282,13 +7284,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>330.0</v>
+        <v>348.0</v>
       </c>
       <c r="O98" s="2">
-        <v>137.0</v>
+        <v>142.0</v>
       </c>
       <c r="P98" s="2">
-        <v>193.0</v>
+        <v>206.0</v>
       </c>
       <c r="Q98" s="2">
         <v>0.0</v>
@@ -7341,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>685.0</v>
+        <v>688.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7353,13 +7355,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>685.0</v>
+        <v>688.0</v>
       </c>
       <c r="O99" s="2">
-        <v>344.0</v>
+        <v>345.0</v>
       </c>
       <c r="P99" s="2">
-        <v>341.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q99" s="2">
         <v>0.0</v>
@@ -7412,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>897.0</v>
+        <v>937.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7424,13 +7426,13 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>897.0</v>
+        <v>937.0</v>
       </c>
       <c r="O100" s="2">
-        <v>385.0</v>
+        <v>398.0</v>
       </c>
       <c r="P100" s="2">
-        <v>512.0</v>
+        <v>539.0</v>
       </c>
       <c r="Q100" s="2">
         <v>0.0</v>
@@ -7554,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>801.0</v>
+        <v>808.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7566,13 +7568,13 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>801.0</v>
+        <v>808.0</v>
       </c>
       <c r="O102" s="2">
-        <v>386.0</v>
+        <v>391.0</v>
       </c>
       <c r="P102" s="2">
-        <v>415.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q102" s="2">
         <v>0.0</v>
@@ -7767,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>674.0</v>
+        <v>685.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7779,10 +7781,10 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>674.0</v>
+        <v>685.0</v>
       </c>
       <c r="O105" s="2">
-        <v>317.0</v>
+        <v>328.0</v>
       </c>
       <c r="P105" s="2">
         <v>357.0</v>
@@ -7794,7 +7796,7 @@
         <v>34.0</v>
       </c>
       <c r="S105" s="2">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
       <c r="T105" s="2">
         <v>0.0</v>
@@ -7806,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7838,7 +7840,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" s="2">
-        <v>701.0</v>
+        <v>715.0</v>
       </c>
       <c r="K106" s="2">
         <v>1.0</v>
@@ -7850,13 +7852,13 @@
         <v>0.0</v>
       </c>
       <c r="N106" s="2">
-        <v>701.0</v>
+        <v>715.0</v>
       </c>
       <c r="O106" s="2">
-        <v>293.0</v>
+        <v>302.0</v>
       </c>
       <c r="P106" s="2">
-        <v>398.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q106" s="2">
         <v>10.0</v>
@@ -7865,10 +7867,10 @@
         <v>31.0</v>
       </c>
       <c r="S106" s="2">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="T106" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="U106" s="2">
         <v>1.0</v>
@@ -7877,7 +7879,7 @@
         <v>0.0</v>
       </c>
       <c r="W106" s="2">
-        <v>93.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -7909,7 +7911,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>405.0</v>
+        <v>429.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7918,16 +7920,16 @@
         <v>1.0</v>
       </c>
       <c r="M107" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N107" s="2">
-        <v>403.0</v>
+        <v>426.0</v>
       </c>
       <c r="O107" s="2">
-        <v>174.0</v>
+        <v>182.0</v>
       </c>
       <c r="P107" s="2">
-        <v>231.0</v>
+        <v>247.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -8081,7 +8083,7 @@
         <v>5.0</v>
       </c>
       <c r="T109" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U109" s="2">
         <v>0.0</v>
@@ -8090,7 +8092,7 @@
         <v>0.0</v>
       </c>
       <c r="W109" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -8122,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>390.0</v>
+        <v>391.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8134,13 +8136,13 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>390.0</v>
+        <v>391.0</v>
       </c>
       <c r="O110" s="2">
         <v>172.0</v>
       </c>
       <c r="P110" s="2">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
@@ -8406,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>508.0</v>
+        <v>520.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8418,13 +8420,13 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>508.0</v>
+        <v>520.0</v>
       </c>
       <c r="O114" s="2">
-        <v>257.0</v>
+        <v>265.0</v>
       </c>
       <c r="P114" s="2">
-        <v>250.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
@@ -8477,7 +8479,7 @@
         <v>1337.0</v>
       </c>
       <c r="J115" s="2">
-        <v>978.0</v>
+        <v>992.0</v>
       </c>
       <c r="K115" s="2">
         <v>1.0</v>
@@ -8489,13 +8491,13 @@
         <v>0.0</v>
       </c>
       <c r="N115" s="2">
-        <v>978.0</v>
+        <v>992.0</v>
       </c>
       <c r="O115" s="2">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
       <c r="P115" s="2">
-        <v>540.0</v>
+        <v>553.0</v>
       </c>
       <c r="Q115" s="2">
         <v>0.0</v>
@@ -8690,7 +8692,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>578.0</v>
+        <v>594.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8702,13 +8704,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>578.0</v>
+        <v>594.0</v>
       </c>
       <c r="O118" s="2">
-        <v>293.0</v>
+        <v>303.0</v>
       </c>
       <c r="P118" s="2">
-        <v>283.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q118" s="2">
         <v>2.0</v>
@@ -8761,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>573.0</v>
+        <v>579.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8773,19 +8775,19 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>573.0</v>
+        <v>579.0</v>
       </c>
       <c r="O119" s="2">
-        <v>328.0</v>
+        <v>333.0</v>
       </c>
       <c r="P119" s="2">
         <v>242.0</v>
       </c>
       <c r="Q119" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R119" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="S119" s="2">
         <v>7.0</v>
@@ -8800,7 +8802,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8974,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>481.0</v>
+        <v>510.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8986,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>477.0</v>
+        <v>506.0</v>
       </c>
       <c r="O122" s="2">
-        <v>258.0</v>
+        <v>275.0</v>
       </c>
       <c r="P122" s="2">
-        <v>208.0</v>
+        <v>220.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9069,7 +9071,7 @@
         <v>17.0</v>
       </c>
       <c r="R123" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S123" s="2">
         <v>6.0</v>
@@ -9084,7 +9086,7 @@
         <v>0.0</v>
       </c>
       <c r="W123" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
@@ -9187,7 +9189,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" s="2">
-        <v>1099.0</v>
+        <v>1135.0</v>
       </c>
       <c r="K125" s="2">
         <v>1.0</v>
@@ -9199,16 +9201,16 @@
         <v>0.0</v>
       </c>
       <c r="N125" s="2">
-        <v>1099.0</v>
+        <v>1135.0</v>
       </c>
       <c r="O125" s="2">
-        <v>512.0</v>
+        <v>519.0</v>
       </c>
       <c r="P125" s="2">
-        <v>542.0</v>
+        <v>565.0</v>
       </c>
       <c r="Q125" s="2">
-        <v>45.0</v>
+        <v>51.0</v>
       </c>
       <c r="R125" s="2">
         <v>0.0</v>
@@ -9329,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>697.0</v>
+        <v>707.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9341,13 +9343,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>697.0</v>
+        <v>707.0</v>
       </c>
       <c r="O127" s="2">
-        <v>442.0</v>
+        <v>448.0</v>
       </c>
       <c r="P127" s="2">
-        <v>255.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
@@ -9359,7 +9361,7 @@
         <v>13.0</v>
       </c>
       <c r="T127" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U127" s="2">
         <v>0.0</v>
@@ -9368,7 +9370,7 @@
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9400,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>799.0</v>
+        <v>805.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9412,10 +9414,10 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>799.0</v>
+        <v>805.0</v>
       </c>
       <c r="O128" s="2">
-        <v>422.0</v>
+        <v>428.0</v>
       </c>
       <c r="P128" s="2">
         <v>375.0</v>
@@ -9471,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>442.0</v>
+        <v>444.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9483,10 +9485,10 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>442.0</v>
+        <v>444.0</v>
       </c>
       <c r="O129" s="2">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="P129" s="2">
         <v>189.0</v>
@@ -9542,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>507.0</v>
+        <v>518.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9554,16 +9556,16 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>505.0</v>
+        <v>516.0</v>
       </c>
       <c r="O130" s="2">
-        <v>327.0</v>
+        <v>337.0</v>
       </c>
       <c r="P130" s="2">
         <v>160.0</v>
       </c>
       <c r="Q130" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R130" s="2">
         <v>6.0</v>
@@ -9572,7 +9574,7 @@
         <v>0.0</v>
       </c>
       <c r="T130" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="U130" s="2">
         <v>0.0</v>
@@ -9581,7 +9583,7 @@
         <v>0.0</v>
       </c>
       <c r="W130" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
@@ -9613,7 +9615,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>482.0</v>
+        <v>491.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9625,13 +9627,13 @@
         <v>5.0</v>
       </c>
       <c r="N131" s="2">
-        <v>477.0</v>
+        <v>486.0</v>
       </c>
       <c r="O131" s="2">
-        <v>260.0</v>
+        <v>267.0</v>
       </c>
       <c r="P131" s="2">
-        <v>211.0</v>
+        <v>213.0</v>
       </c>
       <c r="Q131" s="2">
         <v>11.0</v>
@@ -9755,7 +9757,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" s="2">
-        <v>668.0</v>
+        <v>674.0</v>
       </c>
       <c r="K133" s="2">
         <v>1.0</v>
@@ -9767,13 +9769,13 @@
         <v>0.0</v>
       </c>
       <c r="N133" s="2">
-        <v>668.0</v>
+        <v>674.0</v>
       </c>
       <c r="O133" s="2">
-        <v>347.0</v>
+        <v>351.0</v>
       </c>
       <c r="P133" s="2">
-        <v>310.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q133" s="2">
         <v>11.0</v>
@@ -10039,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>417.0</v>
+        <v>442.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10051,19 +10053,19 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>417.0</v>
+        <v>442.0</v>
       </c>
       <c r="O137" s="2">
-        <v>158.0</v>
+        <v>172.0</v>
       </c>
       <c r="P137" s="2">
-        <v>246.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q137" s="2">
         <v>13.0</v>
       </c>
       <c r="R137" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="S137" s="2">
         <v>6.0</v>
@@ -10072,13 +10074,13 @@
         <v>0.0</v>
       </c>
       <c r="U137" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V137" s="2">
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10134,10 +10136,10 @@
         <v>24.0</v>
       </c>
       <c r="R138" s="2">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="S138" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T138" s="2">
         <v>0.0</v>
@@ -10149,7 +10151,7 @@
         <v>0.0</v>
       </c>
       <c r="W138" s="2">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -10181,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>708.0</v>
+        <v>724.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10193,13 +10195,13 @@
         <v>1.0</v>
       </c>
       <c r="N139" s="2">
-        <v>707.0</v>
+        <v>723.0</v>
       </c>
       <c r="O139" s="2">
-        <v>423.0</v>
+        <v>431.0</v>
       </c>
       <c r="P139" s="2">
-        <v>264.0</v>
+        <v>272.0</v>
       </c>
       <c r="Q139" s="2">
         <v>21.0</v>
@@ -10208,7 +10210,7 @@
         <v>16.0</v>
       </c>
       <c r="S139" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="T139" s="2">
         <v>0.0</v>
@@ -10220,7 +10222,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -10252,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>597.0</v>
+        <v>601.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10264,13 +10266,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>597.0</v>
+        <v>601.0</v>
       </c>
       <c r="O140" s="2">
-        <v>292.0</v>
+        <v>294.0</v>
       </c>
       <c r="P140" s="2">
-        <v>304.0</v>
+        <v>306.0</v>
       </c>
       <c r="Q140" s="2">
         <v>1.0</v>
@@ -10323,7 +10325,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>516.0</v>
+        <v>519.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10335,13 +10337,13 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>515.0</v>
+        <v>518.0</v>
       </c>
       <c r="O141" s="2">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="P141" s="2">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
       <c r="Q141" s="2">
         <v>0.0</v>
@@ -10394,7 +10396,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" s="2">
-        <v>818.0</v>
+        <v>833.0</v>
       </c>
       <c r="K142" s="2">
         <v>1.0</v>
@@ -10406,13 +10408,13 @@
         <v>0.0</v>
       </c>
       <c r="N142" s="2">
-        <v>818.0</v>
+        <v>833.0</v>
       </c>
       <c r="O142" s="2">
-        <v>439.0</v>
+        <v>449.0</v>
       </c>
       <c r="P142" s="2">
-        <v>379.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q142" s="2">
         <v>0.0</v>
@@ -10465,7 +10467,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>502.0</v>
+        <v>504.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10477,13 +10479,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>501.0</v>
+        <v>503.0</v>
       </c>
       <c r="O143" s="2">
         <v>293.0</v>
       </c>
       <c r="P143" s="2">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q143" s="2">
         <v>0.0</v>
@@ -10607,7 +10609,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>572.0</v>
+        <v>574.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10619,16 +10621,16 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>572.0</v>
+        <v>574.0</v>
       </c>
       <c r="O145" s="2">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="P145" s="2">
         <v>324.0</v>
       </c>
       <c r="Q145" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R145" s="2">
         <v>12.0</v>
@@ -10749,7 +10751,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>325.0</v>
+        <v>329.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10761,13 +10763,13 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>325.0</v>
+        <v>329.0</v>
       </c>
       <c r="O147" s="2">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="P147" s="2">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="Q147" s="2">
         <v>19.0</v>
@@ -10820,7 +10822,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>562.0</v>
+        <v>566.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10832,13 +10834,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>562.0</v>
+        <v>566.0</v>
       </c>
       <c r="O148" s="2">
-        <v>191.0</v>
+        <v>194.0</v>
       </c>
       <c r="P148" s="2">
-        <v>371.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q148" s="2">
         <v>0.0</v>
@@ -10891,7 +10893,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>374.0</v>
+        <v>396.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10903,13 +10905,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>374.0</v>
+        <v>396.0</v>
       </c>
       <c r="O149" s="2">
-        <v>211.0</v>
+        <v>225.0</v>
       </c>
       <c r="P149" s="2">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="Q149" s="2">
         <v>2.0</v>
@@ -11104,7 +11106,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>504.0</v>
+        <v>517.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11116,13 +11118,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>503.0</v>
+        <v>516.0</v>
       </c>
       <c r="O152" s="2">
-        <v>246.0</v>
+        <v>251.0</v>
       </c>
       <c r="P152" s="2">
-        <v>258.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q152" s="2">
         <v>0.0</v>
@@ -11175,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>690.0</v>
+        <v>700.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11187,13 +11189,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>690.0</v>
+        <v>700.0</v>
       </c>
       <c r="O153" s="2">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
       <c r="P153" s="2">
-        <v>351.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q153" s="2">
         <v>0.0</v>
@@ -11246,7 +11248,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>525.0</v>
+        <v>545.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11258,16 +11260,16 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>525.0</v>
+        <v>545.0</v>
       </c>
       <c r="O154" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="P154" s="2">
-        <v>295.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>201.0</v>
+        <v>208.0</v>
       </c>
       <c r="R154" s="2">
         <v>0.0</v>
@@ -11530,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>627.0</v>
+        <v>630.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11542,13 +11544,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>627.0</v>
+        <v>630.0</v>
       </c>
       <c r="O158" s="2">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="P158" s="2">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11601,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>675.0</v>
+        <v>690.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11613,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>674.0</v>
+        <v>689.0</v>
       </c>
       <c r="O159" s="2">
-        <v>379.0</v>
+        <v>387.0</v>
       </c>
       <c r="P159" s="2">
-        <v>296.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11743,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>531.0</v>
+        <v>578.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11755,19 +11757,19 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>531.0</v>
+        <v>578.0</v>
       </c>
       <c r="O161" s="2">
-        <v>270.0</v>
+        <v>293.0</v>
       </c>
       <c r="P161" s="2">
-        <v>253.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
       </c>
       <c r="R161" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S161" s="2">
         <v>0.0</v>
@@ -11782,7 +11784,7 @@
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -11814,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>661.0</v>
+        <v>679.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11826,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>660.0</v>
+        <v>678.0</v>
       </c>
       <c r="O162" s="2">
         <v>13.0</v>
       </c>
       <c r="P162" s="2">
-        <v>167.0</v>
+        <v>171.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>481.0</v>
+        <v>495.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11885,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>657.0</v>
+        <v>659.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11897,16 +11899,16 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>657.0</v>
+        <v>659.0</v>
       </c>
       <c r="O163" s="2">
         <v>8.0</v>
       </c>
       <c r="P163" s="2">
-        <v>299.0</v>
+        <v>300.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="R163" s="2">
         <v>0.0</v>
@@ -12027,7 +12029,7 @@
         <v>421.0</v>
       </c>
       <c r="J165" s="2">
-        <v>336.0</v>
+        <v>350.0</v>
       </c>
       <c r="K165" s="2">
         <v>1.0</v>
@@ -12039,16 +12041,16 @@
         <v>0.0</v>
       </c>
       <c r="N165" s="2">
-        <v>336.0</v>
+        <v>350.0</v>
       </c>
       <c r="O165" s="2">
-        <v>184.0</v>
+        <v>189.0</v>
       </c>
       <c r="P165" s="2">
-        <v>143.0</v>
+        <v>150.0</v>
       </c>
       <c r="Q165" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R165" s="2">
         <v>9.0</v>
@@ -12060,13 +12062,13 @@
         <v>0.0</v>
       </c>
       <c r="U165" s="2">
-        <v>40.0</v>
+        <v>56.0</v>
       </c>
       <c r="V165" s="2">
         <v>1.0</v>
       </c>
       <c r="W165" s="2">
-        <v>55.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
@@ -12098,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12110,19 +12112,19 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
       <c r="O166" s="2">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="P166" s="2">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
       </c>
       <c r="R166" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S166" s="2">
         <v>0.0</v>
@@ -12137,7 +12139,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -12169,7 +12171,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" s="2">
-        <v>531.0</v>
+        <v>535.0</v>
       </c>
       <c r="K167" s="2">
         <v>1.0</v>
@@ -12181,10 +12183,10 @@
         <v>0.0</v>
       </c>
       <c r="N167" s="2">
-        <v>531.0</v>
+        <v>535.0</v>
       </c>
       <c r="O167" s="2">
-        <v>257.0</v>
+        <v>261.0</v>
       </c>
       <c r="P167" s="2">
         <v>274.0</v>
@@ -12193,7 +12195,7 @@
         <v>0.0</v>
       </c>
       <c r="R167" s="2">
-        <v>16.0</v>
+        <v>26.0</v>
       </c>
       <c r="S167" s="2">
         <v>0.0</v>
@@ -12208,7 +12210,7 @@
         <v>0.0</v>
       </c>
       <c r="W167" s="2">
-        <v>16.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
@@ -12240,7 +12242,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>499.0</v>
+        <v>505.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12252,13 +12254,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>499.0</v>
+        <v>505.0</v>
       </c>
       <c r="O168" s="2">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="P168" s="2">
-        <v>266.0</v>
+        <v>269.0</v>
       </c>
       <c r="Q168" s="2">
         <v>88.0</v>
@@ -12311,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>348.0</v>
+        <v>360.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12323,10 +12325,10 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>348.0</v>
+        <v>360.0</v>
       </c>
       <c r="O169" s="2">
-        <v>141.0</v>
+        <v>153.0</v>
       </c>
       <c r="P169" s="2">
         <v>199.0</v>
@@ -12737,7 +12739,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" s="2">
-        <v>808.0</v>
+        <v>809.0</v>
       </c>
       <c r="K175" s="2">
         <v>1.0</v>
@@ -12749,10 +12751,10 @@
         <v>0.0</v>
       </c>
       <c r="N175" s="2">
-        <v>808.0</v>
+        <v>809.0</v>
       </c>
       <c r="O175" s="2">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="P175" s="2">
         <v>430.0</v>
@@ -12808,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>413.0</v>
+        <v>429.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12820,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>413.0</v>
+        <v>429.0</v>
       </c>
       <c r="O176" s="2">
-        <v>161.0</v>
+        <v>168.0</v>
       </c>
       <c r="P176" s="2">
-        <v>252.0</v>
+        <v>261.0</v>
       </c>
       <c r="Q176" s="2">
         <v>0.0</v>
@@ -12879,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>331.0</v>
+        <v>340.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12891,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>331.0</v>
+        <v>340.0</v>
       </c>
       <c r="O177" s="2">
-        <v>144.0</v>
+        <v>147.0</v>
       </c>
       <c r="P177" s="2">
-        <v>187.0</v>
+        <v>193.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -13021,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>508.0</v>
+        <v>528.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13033,34 +13035,34 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>508.0</v>
+        <v>528.0</v>
       </c>
       <c r="O179" s="2">
-        <v>305.0</v>
+        <v>320.0</v>
       </c>
       <c r="P179" s="2">
-        <v>202.0</v>
+        <v>207.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>12.0</v>
+        <v>37.0</v>
       </c>
       <c r="S179" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="T179" s="2">
         <v>0.0</v>
       </c>
       <c r="U179" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="V179" s="2">
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>13.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13092,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13104,10 +13106,10 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="O180" s="2">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="P180" s="2">
         <v>171.0</v>
@@ -13187,22 +13189,22 @@
         <v>0.0</v>
       </c>
       <c r="R181" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S181" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T181" s="2">
         <v>0.0</v>
       </c>
       <c r="U181" s="2">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="V181" s="2">
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13234,7 +13236,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" s="2">
-        <v>531.0</v>
+        <v>544.0</v>
       </c>
       <c r="K182" s="2">
         <v>1.0</v>
@@ -13246,13 +13248,13 @@
         <v>0.0</v>
       </c>
       <c r="N182" s="2">
-        <v>531.0</v>
+        <v>544.0</v>
       </c>
       <c r="O182" s="2">
-        <v>238.0</v>
+        <v>242.0</v>
       </c>
       <c r="P182" s="2">
-        <v>292.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q182" s="2">
         <v>1.0</v>
@@ -13261,10 +13263,10 @@
         <v>21.0</v>
       </c>
       <c r="S182" s="2">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="T182" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U182" s="2">
         <v>2.0</v>
@@ -13273,7 +13275,7 @@
         <v>0.0</v>
       </c>
       <c r="W182" s="2">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -13447,7 +13449,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>541.0</v>
+        <v>577.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13459,13 +13461,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>541.0</v>
+        <v>577.0</v>
       </c>
       <c r="O185" s="2">
-        <v>267.0</v>
+        <v>292.0</v>
       </c>
       <c r="P185" s="2">
-        <v>274.0</v>
+        <v>285.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13477,7 +13479,7 @@
         <v>11.0</v>
       </c>
       <c r="T185" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U185" s="2">
         <v>0.0</v>
@@ -13486,7 +13488,7 @@
         <v>0.0</v>
       </c>
       <c r="W185" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
@@ -13518,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>572.0</v>
+        <v>597.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13530,16 +13532,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>572.0</v>
+        <v>597.0</v>
       </c>
       <c r="O186" s="2">
         <v>118.0</v>
       </c>
       <c r="P186" s="2">
-        <v>272.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>182.0</v>
+        <v>202.0</v>
       </c>
       <c r="R186" s="2">
         <v>1.0</v>
@@ -13660,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>542.0</v>
+        <v>546.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13672,10 +13674,10 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>542.0</v>
+        <v>546.0</v>
       </c>
       <c r="O188" s="2">
-        <v>158.0</v>
+        <v>162.0</v>
       </c>
       <c r="P188" s="2">
         <v>326.0</v>
@@ -13802,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>668.0</v>
+        <v>683.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13814,25 +13816,25 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>668.0</v>
+        <v>683.0</v>
       </c>
       <c r="O190" s="2">
-        <v>331.0</v>
+        <v>340.0</v>
       </c>
       <c r="P190" s="2">
-        <v>316.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q190" s="2">
         <v>21.0</v>
       </c>
       <c r="R190" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="S190" s="2">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="T190" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U190" s="2">
         <v>1.0</v>
@@ -13841,7 +13843,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" s="2">
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -13873,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>530.0</v>
+        <v>546.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13885,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>530.0</v>
+        <v>546.0</v>
       </c>
       <c r="O191" s="2">
-        <v>214.0</v>
+        <v>224.0</v>
       </c>
       <c r="P191" s="2">
-        <v>283.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -13944,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>321.0</v>
+        <v>330.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13956,22 +13958,22 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>321.0</v>
+        <v>330.0</v>
       </c>
       <c r="O192" s="2">
-        <v>175.0</v>
+        <v>182.0</v>
       </c>
       <c r="P192" s="2">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="Q192" s="2">
         <v>2.0</v>
       </c>
       <c r="R192" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S192" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T192" s="2">
         <v>0.0</v>
@@ -13983,7 +13985,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -14015,7 +14017,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>836.0</v>
+        <v>864.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14027,16 +14029,16 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>836.0</v>
+        <v>864.0</v>
       </c>
       <c r="O193" s="2">
-        <v>270.0</v>
+        <v>288.0</v>
       </c>
       <c r="P193" s="2">
-        <v>401.0</v>
+        <v>407.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>165.0</v>
+        <v>169.0</v>
       </c>
       <c r="R193" s="2">
         <v>0.0</v>
@@ -14157,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14169,16 +14171,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="O195" s="2">
         <v>71.0</v>
       </c>
       <c r="P195" s="2">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="R195" s="2">
         <v>0.0</v>
@@ -14228,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1030.0</v>
+        <v>1089.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14240,13 +14242,13 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1030.0</v>
+        <v>1089.0</v>
       </c>
       <c r="O196" s="2">
-        <v>400.0</v>
+        <v>425.0</v>
       </c>
       <c r="P196" s="2">
-        <v>444.0</v>
+        <v>478.0</v>
       </c>
       <c r="Q196" s="2">
         <v>186.0</v>
@@ -14299,7 +14301,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" s="2">
-        <v>1033.0</v>
+        <v>1058.0</v>
       </c>
       <c r="K197" s="2">
         <v>1.0</v>
@@ -14311,16 +14313,16 @@
         <v>0.0</v>
       </c>
       <c r="N197" s="2">
-        <v>1033.0</v>
+        <v>1058.0</v>
       </c>
       <c r="O197" s="2">
-        <v>570.0</v>
+        <v>592.0</v>
       </c>
       <c r="P197" s="2">
         <v>348.0</v>
       </c>
       <c r="Q197" s="2">
-        <v>115.0</v>
+        <v>118.0</v>
       </c>
       <c r="R197" s="2">
         <v>0.0</v>
@@ -14370,7 +14372,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" s="2">
-        <v>1081.0</v>
+        <v>1122.0</v>
       </c>
       <c r="K198" s="2">
         <v>1.0</v>
@@ -14382,16 +14384,16 @@
         <v>0.0</v>
       </c>
       <c r="N198" s="2">
-        <v>1081.0</v>
+        <v>1122.0</v>
       </c>
       <c r="O198" s="2">
         <v>312.0</v>
       </c>
       <c r="P198" s="2">
-        <v>528.0</v>
+        <v>549.0</v>
       </c>
       <c r="Q198" s="2">
-        <v>241.0</v>
+        <v>261.0</v>
       </c>
       <c r="R198" s="2">
         <v>0.0</v>
@@ -14512,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>441.0</v>
+        <v>471.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14524,13 +14526,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>441.0</v>
+        <v>471.0</v>
       </c>
       <c r="O200" s="2">
-        <v>267.0</v>
+        <v>289.0</v>
       </c>
       <c r="P200" s="2">
-        <v>171.0</v>
+        <v>179.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14539,7 +14541,7 @@
         <v>3.0</v>
       </c>
       <c r="S200" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="T200" s="2">
         <v>1.0</v>
@@ -14551,7 +14553,7 @@
         <v>0.0</v>
       </c>
       <c r="W200" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14583,7 +14585,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>652.0</v>
+        <v>661.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14595,13 +14597,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>652.0</v>
+        <v>661.0</v>
       </c>
       <c r="O201" s="2">
-        <v>338.0</v>
+        <v>342.0</v>
       </c>
       <c r="P201" s="2">
-        <v>310.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q201" s="2">
         <v>4.0</v>
@@ -14616,13 +14618,13 @@
         <v>4.0</v>
       </c>
       <c r="U201" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="V201" s="2">
         <v>1.0</v>
       </c>
       <c r="W201" s="2">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -14725,7 +14727,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>567.0</v>
+        <v>615.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14737,13 +14739,13 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>567.0</v>
+        <v>615.0</v>
       </c>
       <c r="O203" s="2">
-        <v>315.0</v>
+        <v>344.0</v>
       </c>
       <c r="P203" s="2">
-        <v>252.0</v>
+        <v>271.0</v>
       </c>
       <c r="Q203" s="2">
         <v>0.0</v>
@@ -14796,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>382.0</v>
+        <v>405.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14808,13 +14810,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>382.0</v>
+        <v>405.0</v>
       </c>
       <c r="O204" s="2">
-        <v>204.0</v>
+        <v>216.0</v>
       </c>
       <c r="P204" s="2">
-        <v>172.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q204" s="2">
         <v>6.0</v>
@@ -14867,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>310.0</v>
+        <v>330.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14879,16 +14881,16 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>310.0</v>
+        <v>330.0</v>
       </c>
       <c r="O205" s="2">
-        <v>136.0</v>
+        <v>148.0</v>
       </c>
       <c r="P205" s="2">
-        <v>147.0</v>
+        <v>154.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="R205" s="2">
         <v>0.0</v>
@@ -14938,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>573.0</v>
+        <v>620.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14950,13 +14952,13 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>573.0</v>
+        <v>620.0</v>
       </c>
       <c r="O206" s="2">
-        <v>331.0</v>
+        <v>364.0</v>
       </c>
       <c r="P206" s="2">
-        <v>242.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
@@ -15009,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>409.0</v>
+        <v>414.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15021,19 +15023,19 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>409.0</v>
+        <v>414.0</v>
       </c>
       <c r="O207" s="2">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
       <c r="P207" s="2">
-        <v>171.0</v>
+        <v>174.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
       </c>
       <c r="R207" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S207" s="2">
         <v>0.0</v>
@@ -15048,7 +15050,7 @@
         <v>0.0</v>
       </c>
       <c r="W207" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15080,7 +15082,7 @@
         <v>762.0</v>
       </c>
       <c r="J208" s="2">
-        <v>432.0</v>
+        <v>465.0</v>
       </c>
       <c r="K208" s="2">
         <v>1.0</v>
@@ -15092,34 +15094,34 @@
         <v>0.0</v>
       </c>
       <c r="N208" s="2">
-        <v>432.0</v>
+        <v>465.0</v>
       </c>
       <c r="O208" s="2">
         <v>123.0</v>
       </c>
       <c r="P208" s="2">
-        <v>193.0</v>
+        <v>205.0</v>
       </c>
       <c r="Q208" s="2">
-        <v>116.0</v>
+        <v>137.0</v>
       </c>
       <c r="R208" s="2">
         <v>0.0</v>
       </c>
       <c r="S208" s="2">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="T208" s="2">
         <v>1.0</v>
       </c>
       <c r="U208" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="V208" s="2">
         <v>0.0</v>
       </c>
       <c r="W208" s="2">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1">
@@ -15151,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>729.0</v>
+        <v>735.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15163,13 +15165,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>729.0</v>
+        <v>735.0</v>
       </c>
       <c r="O209" s="2">
-        <v>353.0</v>
+        <v>356.0</v>
       </c>
       <c r="P209" s="2">
-        <v>376.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15435,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>555.0</v>
+        <v>562.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15447,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>555.0</v>
+        <v>562.0</v>
       </c>
       <c r="O213" s="2">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="P213" s="2">
-        <v>263.0</v>
+        <v>269.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15530,7 +15532,7 @@
         <v>0.0</v>
       </c>
       <c r="R214" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S214" s="2">
         <v>0.0</v>
@@ -15545,7 +15547,7 @@
         <v>0.0</v>
       </c>
       <c r="W214" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
@@ -15577,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>609.0</v>
+        <v>620.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15589,13 +15591,13 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>609.0</v>
+        <v>620.0</v>
       </c>
       <c r="O215" s="2">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="P215" s="2">
-        <v>382.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
@@ -15648,7 +15650,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" s="2">
-        <v>289.0</v>
+        <v>298.0</v>
       </c>
       <c r="K216" s="2">
         <v>1.0</v>
@@ -15660,13 +15662,13 @@
         <v>0.0</v>
       </c>
       <c r="N216" s="2">
-        <v>289.0</v>
+        <v>298.0</v>
       </c>
       <c r="O216" s="2">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="P216" s="2">
-        <v>121.0</v>
+        <v>128.0</v>
       </c>
       <c r="Q216" s="2">
         <v>14.0</v>
@@ -15719,7 +15721,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>553.0</v>
+        <v>563.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15731,13 +15733,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>553.0</v>
+        <v>563.0</v>
       </c>
       <c r="O217" s="2">
-        <v>237.0</v>
+        <v>244.0</v>
       </c>
       <c r="P217" s="2">
-        <v>316.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q217" s="2">
         <v>0.0</v>
@@ -15790,7 +15792,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>458.0</v>
+        <v>476.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15802,22 +15804,22 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>457.0</v>
+        <v>475.0</v>
       </c>
       <c r="O218" s="2">
-        <v>245.0</v>
+        <v>255.0</v>
       </c>
       <c r="P218" s="2">
-        <v>213.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="S218" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T218" s="2">
         <v>0.0</v>
@@ -15829,7 +15831,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15861,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>623.0</v>
+        <v>673.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15873,34 +15875,34 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>623.0</v>
+        <v>673.0</v>
       </c>
       <c r="O219" s="2">
         <v>102.0</v>
       </c>
       <c r="P219" s="2">
-        <v>269.0</v>
+        <v>294.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>252.0</v>
+        <v>277.0</v>
       </c>
       <c r="R219" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S219" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="T219" s="2">
         <v>2.0</v>
       </c>
       <c r="U219" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V219" s="2">
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -16074,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>544.0</v>
+        <v>565.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16086,16 +16088,16 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>544.0</v>
+        <v>565.0</v>
       </c>
       <c r="O222" s="2">
         <v>126.0</v>
       </c>
       <c r="P222" s="2">
-        <v>228.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>190.0</v>
+        <v>197.0</v>
       </c>
       <c r="R222" s="2">
         <v>0.0</v>
@@ -16216,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>370.0</v>
+        <v>430.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16228,7 +16230,7 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>370.0</v>
+        <v>430.0</v>
       </c>
       <c r="O224" s="2">
         <v>19.0</v>
@@ -16237,10 +16239,10 @@
         <v>33.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>318.0</v>
+        <v>378.0</v>
       </c>
       <c r="R224" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S224" s="2">
         <v>0.0</v>
@@ -16255,7 +16257,7 @@
         <v>0.0</v>
       </c>
       <c r="W224" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
@@ -16287,7 +16289,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" s="2">
-        <v>1190.0</v>
+        <v>1234.0</v>
       </c>
       <c r="K225" s="2">
         <v>1.0</v>
@@ -16299,13 +16301,13 @@
         <v>0.0</v>
       </c>
       <c r="N225" s="2">
-        <v>1190.0</v>
+        <v>1234.0</v>
       </c>
       <c r="O225" s="2">
-        <v>680.0</v>
+        <v>701.0</v>
       </c>
       <c r="P225" s="2">
-        <v>510.0</v>
+        <v>533.0</v>
       </c>
       <c r="Q225" s="2">
         <v>0.0</v>
@@ -16358,7 +16360,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>575.0</v>
+        <v>605.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16370,22 +16372,22 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>575.0</v>
+        <v>605.0</v>
       </c>
       <c r="O226" s="2">
         <v>46.0</v>
       </c>
       <c r="P226" s="2">
-        <v>274.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q226" s="2">
-        <v>255.0</v>
+        <v>275.0</v>
       </c>
       <c r="R226" s="2">
-        <v>16.0</v>
+        <v>30.0</v>
       </c>
       <c r="S226" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="T226" s="2">
         <v>0.0</v>
@@ -16397,7 +16399,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>16.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16642,7 +16644,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16654,16 +16656,16 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="O230" s="2">
         <v>69.0</v>
       </c>
       <c r="P230" s="2">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q230" s="2">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="R230" s="2">
         <v>0.0</v>
@@ -16784,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>492.0</v>
+        <v>501.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16796,16 +16798,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>492.0</v>
+        <v>501.0</v>
       </c>
       <c r="O232" s="2">
         <v>5.0</v>
       </c>
       <c r="P232" s="2">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>418.0</v>
+        <v>424.0</v>
       </c>
       <c r="R232" s="2">
         <v>1.0</v>
@@ -16855,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>401.0</v>
+        <v>419.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16867,16 +16869,16 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>401.0</v>
+        <v>419.0</v>
       </c>
       <c r="O233" s="2">
         <v>81.0</v>
       </c>
       <c r="P233" s="2">
-        <v>198.0</v>
+        <v>208.0</v>
       </c>
       <c r="Q233" s="2">
-        <v>122.0</v>
+        <v>130.0</v>
       </c>
       <c r="R233" s="2">
         <v>3.0</v>
